--- a/apps/api/assets/vocabulary/初中/外研版/外研版初中英语九年级上册.xlsx
+++ b/apps/api/assets/vocabulary/初中/外研版/外研版初中英语九年级上册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D384"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -686,6 +686,16 @@
           <t>in one's opinion</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 据某人意见
@@ -742,6 +752,16 @@
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>millions of</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -928,6 +948,16 @@
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>go through</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1016,6 +1046,16 @@
           <t>fall away</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【宇】(火箭各级的)分开
@@ -1075,6 +1115,16 @@
           <t>on top of</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在…之上；逼近；胜任(工作等)；掌握(情况等)
@@ -1177,6 +1227,16 @@
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>since then</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1261,6 +1321,16 @@
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>all kinds of</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1440,6 +1510,16 @@
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>as soon as</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1809,6 +1889,16 @@
           <t>lay the table</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 摆饭桌
@@ -2104,6 +2194,16 @@
           <t>give up</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 放弃；断绝；投降；自首
@@ -2352,6 +2452,16 @@
           <t>die for</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 熄灭；销声匿迹；消失；(爱情)熄灭
@@ -2460,6 +2570,16 @@
           <t>take care of</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 照看；处理；清除
@@ -2519,6 +2639,16 @@
           <t>at that time</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 在那时
@@ -2530,6 +2660,16 @@
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>on one's own</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -2680,6 +2820,16 @@
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>die of</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3049,6 +3199,16 @@
           <t>a couple of</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">det. 一对
@@ -3176,6 +3336,16 @@
           <t>be worried about</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 担心；为…而担心；为……担心</t>
@@ -3210,6 +3380,16 @@
           <t>on business</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因公
@@ -3313,6 +3493,16 @@
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>hand in</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -3375,6 +3565,16 @@
           <t>all day long</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “all day”的变体
@@ -3530,6 +3730,16 @@
           <t>against the rules</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 违反规定；犯规；违反规则</t>
@@ -3540,6 +3750,16 @@
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>in trouble</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -3627,6 +3847,16 @@
           <t>No entry</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 禁止进入；不准驶入；不准入内</t>
@@ -3639,6 +3869,16 @@
           <t>no good</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 没用；〔美口〕不好
@@ -3650,6 +3890,16 @@
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>no wonder</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -4018,6 +4268,16 @@
           <t>compare ... with ...</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 和…比较[对照]
@@ -4029,6 +4289,16 @@
       <c r="A165" s="2" t="inlineStr">
         <is>
           <t>of all ages</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -4228,6 +4498,16 @@
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>get into the habit of ...</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -4476,6 +4756,16 @@
           <t>last word</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (起裁决性作用的)最后一句话；定论；最后决定权；完美的事物
@@ -4487,6 +4777,16 @@
       <c r="A186" s="2" t="inlineStr">
         <is>
           <t>come round</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -4527,6 +4827,16 @@
           <t>try out</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (采用前)严密试验；筛矿；量(金属的)纯度
@@ -4562,6 +4872,16 @@
           <t>no longer</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不再
@@ -4573,6 +4893,16 @@
       <c r="A191" s="2" t="inlineStr">
         <is>
           <t>be angry with sb.</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -4658,6 +4988,16 @@
           <t>at least</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 至少
@@ -4736,6 +5076,16 @@
       <c r="A199" s="2" t="inlineStr">
         <is>
           <t>pocket money</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -4891,6 +5241,16 @@
           <t>make sense</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (话等)有意义；合理；有道理；讲得通
@@ -4902,6 +5262,16 @@
       <c r="A207" s="2" t="inlineStr">
         <is>
           <t>by the way</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -4987,6 +5357,16 @@
           <t>get into trouble</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 遇到麻烦；卷入纠纷；受责备；未结婚而怀孕
@@ -4998,6 +5378,16 @@
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>run away</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -5084,6 +5474,16 @@
       <c r="A216" s="2" t="inlineStr">
         <is>
           <t>for a time</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -5241,6 +5641,16 @@
           <t>pay for</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 付开销；赔偿(损失)；(为某种过失)付出代价；吃亏
@@ -5324,6 +5734,16 @@
           <t>stand for</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈口〉忍耐；忍受；主张；拥护
@@ -5475,6 +5895,16 @@
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>no way</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -5587,6 +6017,16 @@
           <t>high jump</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 跳高
@@ -5878,6 +6318,16 @@
           <t>suffer from</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 患（某种病），受（某种病痛）折磨; 因…而受罚[苦，损]; 闹; 罹</t>
@@ -5890,6 +6340,16 @@
           <t>first place</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 第一名
@@ -5903,6 +6363,16 @@
           <t>stop sb. doing sth.</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 停止做某事；停止正在做的事；停止正在做的事情</t>
@@ -5913,6 +6383,16 @@
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>stop sb. from doing sth.</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -5976,6 +6456,16 @@
           <t>take pride in</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以…自豪；对…感到满意
@@ -6011,6 +6501,16 @@
       <c r="A260" s="2" t="inlineStr">
         <is>
           <t>put up</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -6114,6 +6614,16 @@
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>thousands of</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -6363,6 +6873,16 @@
           <t>look through</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 浏览；翻查；对…视而不见；看穿
@@ -6398,6 +6918,16 @@
           <t>at a time</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 一次(多少)；同时；曾经；连续
@@ -6409,6 +6939,16 @@
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>by hand</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -6518,6 +7058,16 @@
           <t>in a way</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 在某一点上
@@ -6529,6 +7079,16 @@
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>compare ... to</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
@@ -6752,6 +7312,16 @@
           <t>wait and see</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adj. 观望的；观望的；静候
@@ -6765,6 +7335,16 @@
           <t>here we go</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 我们开始吧；又来了；我们一起开始吧</t>
@@ -6800,6 +7380,16 @@
           <t>according to</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prep. 根据；按照；据（…所说）；按（…所报道）
@@ -6855,6 +7445,16 @@
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>sailing boat</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
@@ -6967,6 +7567,16 @@
           <t>keep sb. away</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 不挨近
@@ -6978,6 +7588,16 @@
       <c r="A307" s="2" t="inlineStr">
         <is>
           <t>keep sth. away</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
@@ -7042,6 +7662,16 @@
           <t>cut sth. off sth.</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 削除；截止；截断(退路等)；割下来
@@ -7098,6 +7728,16 @@
       <c r="A313" s="2" t="inlineStr">
         <is>
           <t>keep a diary</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
@@ -7185,6 +7825,16 @@
           <t>brush sth. off sth.</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 刷去；打发走；摒弃；逃掉
@@ -7198,6 +7848,16 @@
           <t>at the time</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 当时；在那时；在那个时候</t>
@@ -7208,6 +7868,16 @@
       <c r="A319" s="2" t="inlineStr">
         <is>
           <t>be surprised at</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
@@ -7530,6 +8200,16 @@
           <t>you bet</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈口〉肯定
@@ -7541,6 +8221,16 @@
       <c r="A334" s="2" t="inlineStr">
         <is>
           <t>the thing is</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -7743,6 +8433,16 @@
           <t>be in with a chance</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 有机会</t>
@@ -7823,6 +8523,16 @@
           <t>compared with</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 和…比起来
@@ -7834,6 +8544,16 @@
       <c r="A348" s="2" t="inlineStr">
         <is>
           <t>even though</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -7923,6 +8643,16 @@
           <t>protect sth. against sth.</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 防止；陪伴
@@ -8524,6 +9254,16 @@
           <t>tons of</t>
         </is>
       </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 大量；一大堆；许多，无数的，一大堆</t>
